--- a/Tables/TEXT_DATA.xlsx
+++ b/Tables/TEXT_DATA.xlsx
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="C52">
-        <v>2056</v>
+        <v>2119</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="C53">
-        <v>2111</v>
+        <v>2174</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="C54">
-        <v>2115</v>
+        <v>2178</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="C55">
-        <v>2122</v>
+        <v>2185</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="C56">
-        <v>2398</v>
+        <v>2461</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="C57">
-        <v>2400</v>
+        <v>2463</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="C58">
-        <v>2405</v>
+        <v>2468</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="C60">
-        <v>2412</v>
+        <v>2475</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="C61">
-        <v>2413</v>
+        <v>2476</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="C62">
-        <v>2414</v>
+        <v>2477</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="C63">
-        <v>2416</v>
+        <v>2479</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="C64">
-        <v>2417</v>
+        <v>2480</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="C65">
-        <v>2442</v>
+        <v>2505</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="C66">
-        <v>2445</v>
+        <v>2508</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C67">
-        <v>2446</v>
+        <v>2509</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C68">
-        <v>2448</v>
+        <v>2511</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="C69">
-        <v>2481</v>
+        <v>2544</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="C70">
-        <v>2482</v>
+        <v>2545</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="C71">
-        <v>2522</v>
+        <v>2585</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="C72">
-        <v>1775</v>
+        <v>1488</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="C74">
-        <v>1775</v>
+        <v>1838</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="C75">
-        <v>2548</v>
+        <v>2611</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="C76">
-        <v>2548</v>
+        <v>2611</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="C77">
-        <v>2556</v>
+        <v>2619</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="C79">
-        <v>2551</v>
+        <v>2614</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="C80">
-        <v>2563</v>
+        <v>2626</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="C81">
-        <v>2564</v>
+        <v>2627</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="C82">
-        <v>2565</v>
+        <v>2628</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="C83">
-        <v>2567</v>
+        <v>2630</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="C84">
-        <v>2569</v>
+        <v>2632</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="C86">
-        <v>2629</v>
+        <v>2692</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="C87">
-        <v>2633</v>
+        <v>2696</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="C88">
-        <v>2644</v>
+        <v>2707</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="C89">
-        <v>2645</v>
+        <v>2708</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="C90">
-        <v>2696</v>
+        <v>2759</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="C91">
-        <v>2697</v>
+        <v>2760</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="C92">
-        <v>2698</v>
+        <v>2761</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="C93">
-        <v>2713</v>
+        <v>2776</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C94">
-        <v>2714</v>
+        <v>2777</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="C95">
-        <v>2749</v>
+        <v>2812</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="C96">
-        <v>2750</v>
+        <v>2813</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="C97">
-        <v>2751</v>
+        <v>2814</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="C131">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="C132">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="C141">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="C142">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="C52">
-        <v>2056</v>
+        <v>2119</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="C53">
-        <v>2111</v>
+        <v>2174</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -8764,7 +8764,7 @@
         </is>
       </c>
       <c r="C54">
-        <v>2115</v>
+        <v>2178</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="C55">
-        <v>2122</v>
+        <v>2185</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="C56">
-        <v>2398</v>
+        <v>2461</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="C57">
-        <v>2400</v>
+        <v>2463</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="C58">
-        <v>2405</v>
+        <v>2468</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="C60">
-        <v>2412</v>
+        <v>2475</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="C61">
-        <v>2413</v>
+        <v>2476</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="C62">
-        <v>2414</v>
+        <v>2477</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="C63">
-        <v>2416</v>
+        <v>2479</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -9054,7 +9054,7 @@
         </is>
       </c>
       <c r="C64">
-        <v>2417</v>
+        <v>2480</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="C65">
-        <v>2442</v>
+        <v>2505</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -9112,7 +9112,7 @@
         </is>
       </c>
       <c r="C66">
-        <v>2445</v>
+        <v>2508</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="C67">
-        <v>2446</v>
+        <v>2509</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="C68">
-        <v>2448</v>
+        <v>2511</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -9199,7 +9199,7 @@
         </is>
       </c>
       <c r="C69">
-        <v>2481</v>
+        <v>2544</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="C70">
-        <v>2482</v>
+        <v>2545</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="C71">
-        <v>2522</v>
+        <v>2585</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="C72">
-        <v>1775</v>
+        <v>1488</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="C74">
-        <v>1775</v>
+        <v>1838</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -9373,7 +9373,7 @@
         </is>
       </c>
       <c r="C75">
-        <v>2548</v>
+        <v>2611</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="C76">
-        <v>2548</v>
+        <v>2611</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="C77">
-        <v>2556</v>
+        <v>2619</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="C79">
-        <v>2551</v>
+        <v>2614</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -9518,7 +9518,7 @@
         </is>
       </c>
       <c r="C80">
-        <v>2563</v>
+        <v>2626</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="C81">
-        <v>2564</v>
+        <v>2627</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -9576,7 +9576,7 @@
         </is>
       </c>
       <c r="C82">
-        <v>2565</v>
+        <v>2628</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="C83">
-        <v>2567</v>
+        <v>2630</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="C84">
-        <v>2569</v>
+        <v>2632</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -9692,7 +9692,7 @@
         </is>
       </c>
       <c r="C86">
-        <v>2629</v>
+        <v>2692</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="C87">
-        <v>2633</v>
+        <v>2696</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="C88">
-        <v>2644</v>
+        <v>2707</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -9779,7 +9779,7 @@
         </is>
       </c>
       <c r="C89">
-        <v>2645</v>
+        <v>2708</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -9808,7 +9808,7 @@
         </is>
       </c>
       <c r="C90">
-        <v>2696</v>
+        <v>2759</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -9837,7 +9837,7 @@
         </is>
       </c>
       <c r="C91">
-        <v>2697</v>
+        <v>2760</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="C92">
-        <v>2698</v>
+        <v>2761</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="C93">
-        <v>2713</v>
+        <v>2776</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="C94">
-        <v>2714</v>
+        <v>2777</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="C95">
-        <v>2749</v>
+        <v>2812</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="C96">
-        <v>2750</v>
+        <v>2813</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -10011,7 +10011,7 @@
         </is>
       </c>
       <c r="C97">
-        <v>2751</v>
+        <v>2814</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -10997,7 +10997,7 @@
         </is>
       </c>
       <c r="C131">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -11026,7 +11026,7 @@
         </is>
       </c>
       <c r="C132">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -11287,7 +11287,7 @@
         </is>
       </c>
       <c r="C141">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -11316,7 +11316,7 @@
         </is>
       </c>
       <c r="C142">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D142">
         <v>0</v>

--- a/Tables/TEXT_DATA.xlsx
+++ b/Tables/TEXT_DATA.xlsx
@@ -128,7 +128,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -157,7 +157,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -186,7 +186,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -215,7 +215,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -244,7 +244,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -273,7 +273,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -302,7 +302,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -331,7 +331,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -389,7 +389,7 @@
         </is>
       </c>
       <c r="C13">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>593</v>
+        <v>615</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="C25">
-        <v>596</v>
+        <v>618</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C26">
-        <v>607</v>
+        <v>629</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C27">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>617</v>
+        <v>639</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="C29">
-        <v>656</v>
+        <v>678</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>657</v>
+        <v>679</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>658</v>
+        <v>303</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="C32">
-        <v>659</v>
+        <v>681</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>664</v>
+        <v>686</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>665</v>
+        <v>687</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>666</v>
+        <v>688</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="C37">
-        <v>667</v>
+        <v>689</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>669</v>
+        <v>691</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>669</v>
+        <v>691</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C40">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="C41">
-        <v>674</v>
+        <v>696</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C42">
-        <v>684</v>
+        <v>706</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="C43">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="C44">
-        <v>685</v>
+        <v>707</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="C45">
-        <v>674</v>
+        <v>696</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="C46">
-        <v>686</v>
+        <v>708</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="C47">
-        <v>687</v>
+        <v>709</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="C48">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C49">
-        <v>688</v>
+        <v>710</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="C52">
-        <v>2119</v>
+        <v>2128</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="C53">
-        <v>2174</v>
+        <v>2183</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="C54">
-        <v>2178</v>
+        <v>2187</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="C55">
-        <v>2185</v>
+        <v>2194</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="C56">
-        <v>2461</v>
+        <v>2470</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="C57">
-        <v>2463</v>
+        <v>2472</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="C58">
-        <v>2468</v>
+        <v>2477</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="C60">
-        <v>2475</v>
+        <v>2484</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="C61">
-        <v>2476</v>
+        <v>2485</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="C62">
-        <v>2477</v>
+        <v>2486</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="C63">
-        <v>2479</v>
+        <v>2488</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="C64">
-        <v>2480</v>
+        <v>2489</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="C65">
-        <v>2505</v>
+        <v>2514</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="C66">
-        <v>2508</v>
+        <v>2517</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C67">
-        <v>2509</v>
+        <v>2518</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C68">
-        <v>2511</v>
+        <v>2520</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="C69">
-        <v>2544</v>
+        <v>2553</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="C70">
-        <v>2545</v>
+        <v>2554</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="C71">
-        <v>2585</v>
+        <v>2594</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="C72">
-        <v>1488</v>
+        <v>1497</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="C74">
-        <v>1838</v>
+        <v>1847</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="C75">
-        <v>2611</v>
+        <v>2620</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="C76">
-        <v>2611</v>
+        <v>2620</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="C77">
-        <v>2619</v>
+        <v>2628</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="C79">
-        <v>2614</v>
+        <v>2623</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="C80">
-        <v>2626</v>
+        <v>2635</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="C81">
-        <v>2627</v>
+        <v>2636</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="C82">
-        <v>2628</v>
+        <v>2637</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="C83">
-        <v>2630</v>
+        <v>2639</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="C84">
-        <v>2632</v>
+        <v>2641</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="C86">
-        <v>2692</v>
+        <v>2701</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="C87">
-        <v>2696</v>
+        <v>2705</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="C88">
-        <v>2707</v>
+        <v>2716</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="C89">
-        <v>2708</v>
+        <v>2717</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="C90">
-        <v>2759</v>
+        <v>2768</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="C91">
-        <v>2760</v>
+        <v>2769</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="C92">
-        <v>2761</v>
+        <v>2770</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="C93">
-        <v>2776</v>
+        <v>2785</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C94">
-        <v>2777</v>
+        <v>2786</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="C95">
-        <v>2812</v>
+        <v>2821</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="C96">
-        <v>2813</v>
+        <v>2822</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="C97">
-        <v>2814</v>
+        <v>2823</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="C141">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="C142">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="C175">
-        <v>782</v>
+        <v>811</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="C176">
-        <v>897</v>
+        <v>926</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="C177">
-        <v>979</v>
+        <v>1008</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="C178">
-        <v>1554</v>
+        <v>1583</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="C179">
-        <v>1555</v>
+        <v>1584</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -5232,7 +5232,7 @@
         </is>
       </c>
       <c r="C180">
-        <v>1576</v>
+        <v>1605</v>
       </c>
       <c r="D180">
         <v>1</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="C181">
-        <v>1581</v>
+        <v>1610</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="C182">
-        <v>1582</v>
+        <v>1611</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="C183">
-        <v>1583</v>
+        <v>1612</v>
       </c>
       <c r="D183">
         <v>1</v>
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="C184">
-        <v>1886</v>
+        <v>1915</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="C186">
-        <v>1887</v>
+        <v>1916</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="C187">
-        <v>1887</v>
+        <v>1916</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="C188">
-        <v>889</v>
+        <v>918</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="C190">
-        <v>2406</v>
+        <v>2444</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="C192">
-        <v>2453</v>
+        <v>2491</v>
       </c>
       <c r="D192">
         <v>0</v>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="C193">
-        <v>2454</v>
+        <v>2492</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="C194">
-        <v>2463</v>
+        <v>2501</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="C195">
-        <v>2396</v>
+        <v>2434</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C198">
-        <v>3306</v>
+        <v>3344</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="C199">
-        <v>3307</v>
+        <v>3345</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="C201">
-        <v>2760</v>
+        <v>2798</v>
       </c>
       <c r="D201">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="C203">
-        <v>3955</v>
+        <v>3993</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="C204">
-        <v>3963</v>
+        <v>4001</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="C205">
-        <v>3976</v>
+        <v>4014</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="C206">
-        <v>3979</v>
+        <v>4017</v>
       </c>
       <c r="D206">
         <v>1</v>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="C208">
-        <v>4000</v>
+        <v>4038</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="C209">
-        <v>3985</v>
+        <v>4023</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="C212">
-        <v>1806</v>
+        <v>1835</v>
       </c>
       <c r="D212">
         <v>0</v>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="C213">
-        <v>4067</v>
+        <v>4105</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="C214">
-        <v>4068</v>
+        <v>4106</v>
       </c>
       <c r="D214">
         <v>1</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="C215">
-        <v>4069</v>
+        <v>4107</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -6305,7 +6305,7 @@
         </is>
       </c>
       <c r="C217">
-        <v>4119</v>
+        <v>4157</v>
       </c>
       <c r="D217">
         <v>0</v>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="C218">
-        <v>4142</v>
+        <v>4180</v>
       </c>
       <c r="D218">
         <v>1</v>
@@ -6363,7 +6363,7 @@
         </is>
       </c>
       <c r="C219">
-        <v>4158</v>
+        <v>4196</v>
       </c>
       <c r="D219">
         <v>0</v>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="C220">
-        <v>4161</v>
+        <v>4199</v>
       </c>
       <c r="D220">
         <v>1</v>
@@ -6421,7 +6421,7 @@
         </is>
       </c>
       <c r="C221">
-        <v>961</v>
+        <v>990</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="C223">
-        <v>2260</v>
+        <v>2298</v>
       </c>
       <c r="D223">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="C225">
-        <v>4416</v>
+        <v>4454</v>
       </c>
       <c r="D225">
         <v>0</v>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="C226">
-        <v>4396</v>
+        <v>4434</v>
       </c>
       <c r="D226">
         <v>0</v>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="C227">
-        <v>4470</v>
+        <v>4508</v>
       </c>
       <c r="D227">
         <v>0</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -7459,7 +7459,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -7488,7 +7488,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -7575,7 +7575,7 @@
         </is>
       </c>
       <c r="C13">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -7662,7 +7662,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -7778,7 +7778,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -7894,7 +7894,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>593</v>
+        <v>615</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="C25">
-        <v>596</v>
+        <v>618</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="C26">
-        <v>607</v>
+        <v>629</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="C27">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>617</v>
+        <v>639</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="C29">
-        <v>656</v>
+        <v>678</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -8068,7 +8068,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>657</v>
+        <v>679</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>658</v>
+        <v>303</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -8126,7 +8126,7 @@
         </is>
       </c>
       <c r="C32">
-        <v>659</v>
+        <v>681</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -8184,7 +8184,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>664</v>
+        <v>686</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>665</v>
+        <v>687</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -8242,7 +8242,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>666</v>
+        <v>688</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="C37">
-        <v>667</v>
+        <v>689</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>669</v>
+        <v>691</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>669</v>
+        <v>691</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="C40">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="C41">
-        <v>674</v>
+        <v>696</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -8416,7 +8416,7 @@
         </is>
       </c>
       <c r="C42">
-        <v>684</v>
+        <v>706</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C43">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="C44">
-        <v>685</v>
+        <v>707</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="C45">
-        <v>674</v>
+        <v>696</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="C46">
-        <v>686</v>
+        <v>708</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="C47">
-        <v>687</v>
+        <v>709</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="C48">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="C49">
-        <v>688</v>
+        <v>710</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="C52">
-        <v>2119</v>
+        <v>2128</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="C53">
-        <v>2174</v>
+        <v>2183</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -8764,7 +8764,7 @@
         </is>
       </c>
       <c r="C54">
-        <v>2178</v>
+        <v>2187</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="C55">
-        <v>2185</v>
+        <v>2194</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="C56">
-        <v>2461</v>
+        <v>2470</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="C57">
-        <v>2463</v>
+        <v>2472</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -8880,7 +8880,7 @@
         </is>
       </c>
       <c r="C58">
-        <v>2468</v>
+        <v>2477</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="C60">
-        <v>2475</v>
+        <v>2484</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="C61">
-        <v>2476</v>
+        <v>2485</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="C62">
-        <v>2477</v>
+        <v>2486</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="C63">
-        <v>2479</v>
+        <v>2488</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -9054,7 +9054,7 @@
         </is>
       </c>
       <c r="C64">
-        <v>2480</v>
+        <v>2489</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="C65">
-        <v>2505</v>
+        <v>2514</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -9112,7 +9112,7 @@
         </is>
       </c>
       <c r="C66">
-        <v>2508</v>
+        <v>2517</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="C67">
-        <v>2509</v>
+        <v>2518</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="C68">
-        <v>2511</v>
+        <v>2520</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -9199,7 +9199,7 @@
         </is>
       </c>
       <c r="C69">
-        <v>2544</v>
+        <v>2553</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="C70">
-        <v>2545</v>
+        <v>2554</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="C71">
-        <v>2585</v>
+        <v>2594</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="C72">
-        <v>1488</v>
+        <v>1497</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="C74">
-        <v>1838</v>
+        <v>1847</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -9373,7 +9373,7 @@
         </is>
       </c>
       <c r="C75">
-        <v>2611</v>
+        <v>2620</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="C76">
-        <v>2611</v>
+        <v>2620</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="C77">
-        <v>2619</v>
+        <v>2628</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="C79">
-        <v>2614</v>
+        <v>2623</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -9518,7 +9518,7 @@
         </is>
       </c>
       <c r="C80">
-        <v>2626</v>
+        <v>2635</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="C81">
-        <v>2627</v>
+        <v>2636</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -9576,7 +9576,7 @@
         </is>
       </c>
       <c r="C82">
-        <v>2628</v>
+        <v>2637</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="C83">
-        <v>2630</v>
+        <v>2639</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="C84">
-        <v>2632</v>
+        <v>2641</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -9692,7 +9692,7 @@
         </is>
       </c>
       <c r="C86">
-        <v>2692</v>
+        <v>2701</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="C87">
-        <v>2696</v>
+        <v>2705</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="C88">
-        <v>2707</v>
+        <v>2716</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -9779,7 +9779,7 @@
         </is>
       </c>
       <c r="C89">
-        <v>2708</v>
+        <v>2717</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -9808,7 +9808,7 @@
         </is>
       </c>
       <c r="C90">
-        <v>2759</v>
+        <v>2768</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -9837,7 +9837,7 @@
         </is>
       </c>
       <c r="C91">
-        <v>2760</v>
+        <v>2769</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="C92">
-        <v>2761</v>
+        <v>2770</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="C93">
-        <v>2776</v>
+        <v>2785</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="C94">
-        <v>2777</v>
+        <v>2786</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="C95">
-        <v>2812</v>
+        <v>2821</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="C96">
-        <v>2813</v>
+        <v>2822</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -10011,7 +10011,7 @@
         </is>
       </c>
       <c r="C97">
-        <v>2814</v>
+        <v>2823</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -11287,7 +11287,7 @@
         </is>
       </c>
       <c r="C141">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -11316,7 +11316,7 @@
         </is>
       </c>
       <c r="C142">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="C175">
-        <v>782</v>
+        <v>811</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -12302,7 +12302,7 @@
         </is>
       </c>
       <c r="C176">
-        <v>897</v>
+        <v>926</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -12331,7 +12331,7 @@
         </is>
       </c>
       <c r="C177">
-        <v>979</v>
+        <v>1008</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -12360,7 +12360,7 @@
         </is>
       </c>
       <c r="C178">
-        <v>1554</v>
+        <v>1583</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -12389,7 +12389,7 @@
         </is>
       </c>
       <c r="C179">
-        <v>1555</v>
+        <v>1584</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -12418,7 +12418,7 @@
         </is>
       </c>
       <c r="C180">
-        <v>1576</v>
+        <v>1605</v>
       </c>
       <c r="D180">
         <v>1</v>
@@ -12447,7 +12447,7 @@
         </is>
       </c>
       <c r="C181">
-        <v>1581</v>
+        <v>1610</v>
       </c>
       <c r="D181">
         <v>1</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="C182">
-        <v>1582</v>
+        <v>1611</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="C183">
-        <v>1583</v>
+        <v>1612</v>
       </c>
       <c r="D183">
         <v>1</v>
@@ -12534,7 +12534,7 @@
         </is>
       </c>
       <c r="C184">
-        <v>1886</v>
+        <v>1915</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -12592,7 +12592,7 @@
         </is>
       </c>
       <c r="C186">
-        <v>1887</v>
+        <v>1916</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -12621,7 +12621,7 @@
         </is>
       </c>
       <c r="C187">
-        <v>1887</v>
+        <v>1916</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -12650,7 +12650,7 @@
         </is>
       </c>
       <c r="C188">
-        <v>889</v>
+        <v>918</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="C190">
-        <v>2406</v>
+        <v>2444</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -12766,7 +12766,7 @@
         </is>
       </c>
       <c r="C192">
-        <v>2453</v>
+        <v>2491</v>
       </c>
       <c r="D192">
         <v>0</v>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="C193">
-        <v>2454</v>
+        <v>2492</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -12824,7 +12824,7 @@
         </is>
       </c>
       <c r="C194">
-        <v>2463</v>
+        <v>2501</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="C195">
-        <v>2396</v>
+        <v>2434</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -12940,7 +12940,7 @@
         </is>
       </c>
       <c r="C198">
-        <v>3306</v>
+        <v>3344</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -12969,7 +12969,7 @@
         </is>
       </c>
       <c r="C199">
-        <v>3307</v>
+        <v>3345</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -13027,7 +13027,7 @@
         </is>
       </c>
       <c r="C201">
-        <v>2760</v>
+        <v>2798</v>
       </c>
       <c r="D201">
         <v>0</v>
@@ -13085,7 +13085,7 @@
         </is>
       </c>
       <c r="C203">
-        <v>3955</v>
+        <v>3993</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -13114,7 +13114,7 @@
         </is>
       </c>
       <c r="C204">
-        <v>3963</v>
+        <v>4001</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="C205">
-        <v>3976</v>
+        <v>4014</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         </is>
       </c>
       <c r="C206">
-        <v>3979</v>
+        <v>4017</v>
       </c>
       <c r="D206">
         <v>1</v>
@@ -13230,7 +13230,7 @@
         </is>
       </c>
       <c r="C208">
-        <v>4000</v>
+        <v>4038</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -13259,7 +13259,7 @@
         </is>
       </c>
       <c r="C209">
-        <v>3985</v>
+        <v>4023</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -13346,7 +13346,7 @@
         </is>
       </c>
       <c r="C212">
-        <v>1806</v>
+        <v>1835</v>
       </c>
       <c r="D212">
         <v>0</v>
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="C213">
-        <v>4067</v>
+        <v>4105</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -13404,7 +13404,7 @@
         </is>
       </c>
       <c r="C214">
-        <v>4068</v>
+        <v>4106</v>
       </c>
       <c r="D214">
         <v>1</v>
@@ -13433,7 +13433,7 @@
         </is>
       </c>
       <c r="C215">
-        <v>4069</v>
+        <v>4107</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -13491,7 +13491,7 @@
         </is>
       </c>
       <c r="C217">
-        <v>4119</v>
+        <v>4157</v>
       </c>
       <c r="D217">
         <v>0</v>
@@ -13520,7 +13520,7 @@
         </is>
       </c>
       <c r="C218">
-        <v>4142</v>
+        <v>4180</v>
       </c>
       <c r="D218">
         <v>1</v>
@@ -13549,7 +13549,7 @@
         </is>
       </c>
       <c r="C219">
-        <v>4158</v>
+        <v>4196</v>
       </c>
       <c r="D219">
         <v>0</v>
@@ -13578,7 +13578,7 @@
         </is>
       </c>
       <c r="C220">
-        <v>4161</v>
+        <v>4199</v>
       </c>
       <c r="D220">
         <v>1</v>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="C221">
-        <v>961</v>
+        <v>990</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -13665,7 +13665,7 @@
         </is>
       </c>
       <c r="C223">
-        <v>2260</v>
+        <v>2298</v>
       </c>
       <c r="D223">
         <v>0</v>
@@ -13723,7 +13723,7 @@
         </is>
       </c>
       <c r="C225">
-        <v>4416</v>
+        <v>4454</v>
       </c>
       <c r="D225">
         <v>0</v>
@@ -13752,7 +13752,7 @@
         </is>
       </c>
       <c r="C226">
-        <v>4396</v>
+        <v>4434</v>
       </c>
       <c r="D226">
         <v>0</v>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="C227">
-        <v>4470</v>
+        <v>4508</v>
       </c>
       <c r="D227">
         <v>0</v>
